--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/nov-2025.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/nov-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2653,7 +2653,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>761-720-CM25</t>
+          <t>539119-10249-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>Carabineros de Chile - Dirección de Bienestar</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2708,13 +2708,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2641.8</v>
+        <v>4068.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>539119-10249-CM25</t>
+          <t>761-720-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>4068.9</v>
+        <v>2641.8</v>
       </c>
     </row>
     <row r="39">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>242159.0976</v>
+        <v>242159.1</v>
       </c>
     </row>
     <row r="41">
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>245470.344</v>
+        <v>245470.34</v>
       </c>
     </row>
     <row r="43">
@@ -3263,7 +3263,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>537934-14-CM25</t>
+          <t>514862-1032-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3278,22 +3278,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Enviada a Proveedor</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.219.000-3</t>
+          <t>71.234.100-9</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>EMPRESA DE TRANSPORTE DE PASAJEROS METRO S A</t>
+          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARRO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3303,22 +3303,26 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>SEIDOR TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>76.449.580-2</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>998528.4288</v>
+        <v>129944.43</v>
       </c>
     </row>
     <row r="48">
@@ -3385,7 +3389,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>514862-1032-CM25</t>
+          <t>2711-555-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3410,41 +3414,37 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>71.234.100-9</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARRO</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SEIDOR TECHNOLOGIES S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.449.580-2</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>129944.43</v>
+        <v>21548.04</v>
       </c>
     </row>
     <row r="50">
@@ -3511,7 +3511,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2711-555-CM25</t>
+          <t>387-792-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3531,22 +3531,22 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3566,13 +3566,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>21548.04</v>
+        <v>8877.4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2827-927-CM25</t>
+          <t>761-719-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3597,43 +3597,47 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.120.100-7</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>XERTICA CHILE SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>77.223.453-8</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>4437.51</v>
+        <v>100143.74</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>387-792-CM25</t>
+          <t>872-615-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3653,32 +3657,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>82.983.100-7</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>COMISION CHILENA DE ENERGIA NUCLEAR</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3688,13 +3692,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>8877.4</v>
+        <v>2326.09</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>528208-240-CM25</t>
+          <t>2827-927-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3714,52 +3718,48 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Solicitud de Cancelacion</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.254.200-2</t>
+          <t>69.120.100-7</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>150118.5</v>
+        <v>4437.51</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>761-719-CM25</t>
+          <t>870-380-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>60.718.000-8</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>COMISION NACIONAL DE RIEGO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3799,32 +3799,28 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>XERTICA CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>77.223.453-8</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>100143.736</v>
+        <v>38478.65</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>872-615-CM25</t>
+          <t>1305552-147-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3839,22 +3835,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>82.983.100-7</t>
+          <t>61.981.030-9</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>COMISION CHILENA DE ENERGIA NUCLEAR</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3864,12 +3860,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3879,13 +3875,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2326.09</v>
+        <v>2548.69</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3696-477-CM25</t>
+          <t>4955-154-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3910,17 +3906,17 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>60.505.000-k</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>Carabineros de Chile - Dirección General</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3940,13 +3936,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>3171.77</v>
+        <v>1480.16</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3861-262-CM25</t>
+          <t>1385462-236-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3966,32 +3962,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.191.400-3</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOLTEN</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -4001,13 +3997,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1594.6</v>
+        <v>61275.86</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2832-3466-CM25</t>
+          <t>3861-262-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4027,32 +4023,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.260.400-8</t>
+          <t>69.191.400-3</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILLOTA</t>
+          <t>I MUNICIPALIDAD DE TOLTEN</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4062,13 +4058,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>7189.74</v>
+        <v>1594.6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4955-154-CM25</t>
+          <t>3696-477-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4093,17 +4089,17 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección General</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4123,13 +4119,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1480.16</v>
+        <v>3171.77</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1385462-236-CM25</t>
+          <t>2832-3466-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4154,27 +4150,27 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>69.260.400-8</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>I MUNICIPALIDAD DE QUILLOTA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4184,13 +4180,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>61275.86</v>
+        <v>7189.74</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1305552-147-CM25</t>
+          <t>539119-10496-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4205,7 +4201,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4215,12 +4211,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.981.030-9</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
+          <t>Carabineros de Chile - Dirección de Bienestar</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4230,12 +4226,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4245,13 +4241,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2548.69</v>
+        <v>845.85</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>870-380-CM25</t>
+          <t>4455-1025-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4266,7 +4262,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4276,27 +4272,27 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>60.718.000-8</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE RIEGO</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4306,13 +4302,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>38478.65</v>
+        <v>1903.17</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>539119-10496-CM25</t>
+          <t>857-221-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4327,7 +4323,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4337,12 +4333,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>72.576.700-5</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>Servicio Nacional de la Discapacidad</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4352,12 +4348,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4367,13 +4363,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>845.85</v>
+        <v>19796.96</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4455-1025-CM25</t>
+          <t>2776-990-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4388,7 +4384,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4398,27 +4394,27 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4428,13 +4424,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1903.17</v>
+        <v>26632.2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5416-1478-CM25</t>
+          <t>577290-220-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4459,27 +4455,27 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.979.750-7</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>Subsecretaria de Transportes</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>NextTime Software S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>99.576.370-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4489,13 +4485,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1486.91</v>
+        <v>25374.13</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>857-221-CM25</t>
+          <t>5416-1478-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4520,27 +4516,27 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>72.576.700-5</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Servicio Nacional de la Discapacidad</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>NextTime Software S.A.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>99.576.370-2</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4550,13 +4546,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>19796.96</v>
+        <v>1486.91</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2776-990-CM25</t>
+          <t>1305527-55-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4571,7 +4567,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4581,27 +4577,27 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>61.981.090-2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL PINO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4611,128 +4607,6 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>26632.2</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>577290-220-CM25</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>nov-2025</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>61.979.750-7</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Subsecretaria de Transportes</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="n">
-        <v>25374.13</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>1305527-55-CM25</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>nov-2025</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>61.981.090-2</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL PINO</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Inversiones Hebo Limitada</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>77.553.790-6</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="n">
         <v>19535.04</v>
       </c>
     </row>
